--- a/docs/figures/gcd/figure-data.xlsx
+++ b/docs/figures/gcd/figure-data.xlsx
@@ -11,16 +11,18 @@
     <sheet name="Entry probabilities" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="W1 trace" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Termination" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Sources" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Read me" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Judging audit" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Sources" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Read me" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Outcomes'!$A$1:$G$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Entry probabilities'!$A$1:$C$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'W1 trace'!$A$1:$D$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Termination'!$A$1:$E$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Sources'!$A$1:$D$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Read me'!$A$1:$B$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Judging audit'!$A$1:$H$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Sources'!$A$1:$D$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Read me'!$A$1:$B$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -2323,7 +2325,290 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="33" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Model label</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Stratum</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Input over 2500 characters</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Degenerate and token-limited</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Fulfillment with invalid output</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Token counts at limit</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Artificial cutoff cited by state</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Judge errors</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>DeepSeek-V4</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>adversarial</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>463</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27</v>
+      </c>
+      <c r="E2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>{"800": 321}</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>{"degenerate": 2}</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>DeepSeek-V4</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>508</v>
+      </c>
+      <c r="D3" t="n">
+        <v>58</v>
+      </c>
+      <c r="E3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>{"800": 502}</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>{"degenerate": 11}</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gemma-4-26B</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>adversarial</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>395</v>
+      </c>
+      <c r="D4" t="n">
+        <v>16</v>
+      </c>
+      <c r="E4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>{"800": 142}</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>{"degenerate": 3}</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>{"HTTP Error 500: Internal Server Error": 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gemma-4-26B</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>508</v>
+      </c>
+      <c r="D5" t="n">
+        <v>66</v>
+      </c>
+      <c r="E5" t="n">
+        <v>17</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>{"800": 502}</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>{"degenerate": 10, "valid_fulfillment": 1}</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>{"HTTP Error 500: Internal Server Error": 3}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Qwen3.8-27B</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>adversarial</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>151</v>
+      </c>
+      <c r="D6" t="n">
+        <v>15</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>{"800": 102}</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>{"degenerate": 1}</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>{"cross-field invariant violated": 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Qwen3.8-27B</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>324</v>
+      </c>
+      <c r="D7" t="n">
+        <v>44</v>
+      </c>
+      <c r="E7" t="n">
+        <v>8</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>{"800": 314}</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>{"degenerate": 4}</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H7"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -2663,16 +2948,16 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>scripts/grammar_probe/gate_full.py</t>
+          <t>scripts/grammar_probe/report.py</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>90c9cc9720b0298c04d40679e4893fd9e289bfbb13ed64360b5674162ba5c3e7</t>
+          <t>554fd927b4ae84c375d30e1bf1af7a388eceac89e366b8dbe3cf98d1aa2a34b3</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3152</v>
+        <v>3333</v>
       </c>
       <c r="D19" t="b">
         <v>1</v>
@@ -2681,16 +2966,16 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>scripts/grammar_probe/battery_gcd.py</t>
+          <t>scripts/grammar_probe/METHODS.md</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>8518ee6872d7d49c35dbed1f01ca5f4ed23b47f5f22ae574468775497d9dc7d1</t>
+          <t>7d70ec137f6fdc4755cd2ef95f4773497f32ed83a5c41b12a7d19fd00b6601e9</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4835</v>
+        <v>2813</v>
       </c>
       <c r="D20" t="b">
         <v>1</v>
@@ -2699,16 +2984,16 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>scripts/grammar_probe/SPOT_CHECK_RESULTS.md</t>
+          <t>scripts/grammar_probe/gate_full.py</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>9457973467a669d8c8529265c7f2f7d242fe91247c7ed4ac093c3088e8f5629b</t>
+          <t>90c9cc9720b0298c04d40679e4893fd9e289bfbb13ed64360b5674162ba5c3e7</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1848</v>
+        <v>3152</v>
       </c>
       <c r="D21" t="b">
         <v>1</v>
@@ -2717,16 +3002,16 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>src/serve/api/grammar/gcd_w1.gbnf</t>
+          <t>scripts/grammar_probe/battery_gcd.py</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>d396cb0fd5a954f9263f49fa65810eaffd04ef10d684a4f2fb6a68a7058a8c77</t>
+          <t>8518ee6872d7d49c35dbed1f01ca5f4ed23b47f5f22ae574468775497d9dc7d1</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>84794</v>
+        <v>4835</v>
       </c>
       <c r="D22" t="b">
         <v>1</v>
@@ -2735,16 +3020,16 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>src/serve/api/handlers.rs</t>
+          <t>scripts/grammar_probe/SPOT_CHECK_RESULTS.md</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>945b9cc6958d3bdb58e3357e166cbdedf55b6f769d99a31d564f208acd458841</t>
+          <t>9457973467a669d8c8529265c7f2f7d242fe91247c7ed4ac093c3088e8f5629b</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>571003</v>
+        <v>1848</v>
       </c>
       <c r="D23" t="b">
         <v>1</v>
@@ -2753,16 +3038,16 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>src/serve/api/engine.rs</t>
+          <t>src/serve/api/grammar/gcd_w1.gbnf</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5a9d6c9caca1f09724ce3dbf85e64a8f4f9cb2799988f941f5cc793ce5c76b34</t>
+          <t>d396cb0fd5a954f9263f49fa65810eaffd04ef10d684a4f2fb6a68a7058a8c77</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2584514</v>
+        <v>84794</v>
       </c>
       <c r="D24" t="b">
         <v>1</v>
@@ -2771,16 +3056,16 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>src/serve/sampler_pure.rs</t>
+          <t>src/serve/api/handlers.rs</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5808fb7eec34cba0a49de2a80e2a051f97d989824ed74948dfd9c99518a3d998</t>
+          <t>945b9cc6958d3bdb58e3357e166cbdedf55b6f769d99a31d564f208acd458841</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>47694</v>
+        <v>571003</v>
       </c>
       <c r="D25" t="b">
         <v>1</v>
@@ -2789,16 +3074,16 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>src/inference/models/deepseek4/ffn_forward.rs</t>
+          <t>src/serve/api/engine.rs</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>4940ef805bfbef63a2c17ad3bc0b2376f5baab9a8f8e1d8ec7b0d4c4089970c7</t>
+          <t>5a9d6c9caca1f09724ce3dbf85e64a8f4f9cb2799988f941f5cc793ce5c76b34</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>25914</v>
+        <v>2584514</v>
       </c>
       <c r="D26" t="b">
         <v>1</v>
@@ -2807,16 +3092,16 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>src/inference/models/qwen35/forward_gpu.rs</t>
+          <t>src/serve/sampler_pure.rs</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>38395960690f8a1e7ff9cc4a16a9689db0faa52d1888442192b733c32ad68966</t>
+          <t>5808fb7eec34cba0a49de2a80e2a051f97d989824ed74948dfd9c99518a3d998</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>556404</v>
+        <v>47694</v>
       </c>
       <c r="D27" t="b">
         <v>1</v>
@@ -2825,16 +3110,16 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>src/calibrate/mod.rs</t>
+          <t>src/inference/models/deepseek4/ffn_forward.rs</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>b8bc42854f49c0afcbf6285ec65f2e13a752d9efeb5fab2c4171120852d9b684</t>
+          <t>4940ef805bfbef63a2c17ad3bc0b2376f5baab9a8f8e1d8ec7b0d4c4089970c7</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>16015</v>
+        <v>25914</v>
       </c>
       <c r="D28" t="b">
         <v>1</v>
@@ -2843,34 +3128,70 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>examples/recon-opportunities.schema.json</t>
+          <t>src/inference/models/qwen35/forward_gpu.rs</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5890c09e6f827cdcd6b2148c119f782f2400d02d42dc952d882c60105f340f04</t>
+          <t>38395960690f8a1e7ff9cc4a16a9689db0faa52d1888442192b733c32ad68966</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3255</v>
+        <v>556404</v>
       </c>
       <c r="D29" t="b">
         <v>1</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>src/calibrate/mod.rs</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>b8bc42854f49c0afcbf6285ec65f2e13a752d9efeb5fab2c4171120852d9b684</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>16015</v>
+      </c>
+      <c r="D30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>examples/recon-opportunities.schema.json</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>5890c09e6f827cdcd6b2148c119f782f2400d02d42dc952d882c60105f340f04</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>3255</v>
+      </c>
+      <c r="D31" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D29"/>
+  <autoFilter ref="A1:D31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2976,17 +3297,53 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Limitation</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>The judging harness clips input at 2500 characters and does not pass generation finish metadata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Limitation</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Response-state labels can contradict output_validity; original categories are preserved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Limitation</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>No matched full-corpus unconstrained baseline was found in the retained W1 records.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>Concept figures</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Generation loop and GLP projection are explanatory, not empirical</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B9"/>
+  <autoFilter ref="A1:B12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/figures/gcd/figure-data.xlsx
+++ b/docs/figures/gcd/figure-data.xlsx
@@ -13,7 +13,12 @@
     <sheet name="Termination" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Judging audit" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Sources" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Read me" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Termination cross-tabs" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="GLP panel" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="GLP paired transitions" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Battery attempts" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Follow-up sources" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Read me" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Outcomes'!$A$1:$G$30</definedName>
@@ -22,7 +27,12 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Termination'!$A$1:$E$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Judging audit'!$A$1:$H$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Sources'!$A$1:$D$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Read me'!$A$1:$B$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Termination cross-tabs'!$A$1:$E$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'GLP panel'!$A$1:$I$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'GLP paired transitions'!$A$1:$E$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Battery attempts'!$A$1:$G$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Follow-up sources'!$A$1:$D$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Read me'!$A$1:$B$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1421,6 +1431,1557 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Attempt</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Rows</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>First timestamp</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Last timestamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>17</v>
+      </c>
+      <c r="C2" t="n">
+        <v>14</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1789034017.26239</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1789034198.881141</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C3" t="n">
+        <v>15</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1789034475.046275</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1789034712.862478</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>17</v>
+      </c>
+      <c r="C4" t="n">
+        <v>16</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1789034765.90544</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1789035101.706308</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>17</v>
+      </c>
+      <c r="C5" t="n">
+        <v>17</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1789035123.50756</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1789035449.135897</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D60"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="70" customWidth="1" min="1" max="1"/>
+    <col width="66" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Path</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>SHA-256</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Bytes</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Identity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>scripts/grammar_probe/full_results_w1.jsonl</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>b5a68b3f72dcf825219623ef46762dfd463c021ac40d140ff23e2a3c3f4e7297</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>3817886</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>historical snapshot</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>scripts/grammar_probe/full_verdicts_w1.jsonl</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>a0ec7f4bd0e1014d02b739963e1c5fdf862e343416b06fef5f2690ea5a127e15</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>428283</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>historical snapshot</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>scripts/grammar_probe/full_results_w1.truncation-report.json</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>d29c56070f095716bb6c52fb257ddaeda260bb9093c6c707290214a3ff8fe68f</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1068</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>294907cd655ee81eedb8d8b9ea30ab80ade483bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>scripts/grammar_probe/spike_results_w1_gemma.jsonl</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>80a75f2bba863590008decb8e188d916c0846f0c15698145a70c2ff4666b9399</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>3506418</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>historical snapshot</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>scripts/grammar_probe/spike_verdicts_w1_gemma.jsonl</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>3e531f4f804b6383cb90ae8be923ae85541c9afdb8fad81e025e0946a73d118f</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>424027</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>historical snapshot</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>scripts/grammar_probe/spike_results_w1_gemma.truncation-report.json</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>bca43eb05bd4c6f2db0d6c94f4fb6eae546e8d4735af30d90387d51b20d8118d</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1039</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>294907cd655ee81eedb8d8b9ea30ab80ade483bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>scripts/grammar_probe/spike_results_w1_qwen38.jsonl</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ebfe743af8b130376c79ee7ffa8f7bd97df2ed695754dbead84e42451a0cea22</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2440924</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>historical snapshot</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>scripts/grammar_probe/spike_verdicts_w1_qwen38.jsonl</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ce39d374f234190ad667a9accc6e1b9ef86e538c0ce0fdcb8fb970040dad7162</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>421736</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>historical snapshot</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>scripts/grammar_probe/spike_results_w1_qwen38.truncation-report.json</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>9de70981983b18e1f78053e04e5ad8d65e44b5873972662f9b7c1b6243c87382</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1085</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>294907cd655ee81eedb8d8b9ea30ab80ade483bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>scripts/grammar_probe/gate34/baseline/results.jsonl</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>368d9f03ad3aed2758901680fc50b34d44731fe0ce9276ca1ea107aa402c04c3</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>47668</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>294907cd655ee81eedb8d8b9ea30ab80ade483bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>scripts/grammar_probe/gate34/baseline/verdicts.jsonl</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>00be8615ccb26acc57e20ca0a1d517e60f3fd17ea934055db346bb0f76906635</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>18244</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>294907cd655ee81eedb8d8b9ea30ab80ade483bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>scripts/grammar_probe/gate34/baseline/meta.json</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>c9d5c56ec9cc30ebf0b3d7e95cd7d4f8e7fb5ada3012d352b5ace92315a3d389</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>506</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>294907cd655ee81eedb8d8b9ea30ab80ade483bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>scripts/grammar_probe/gate34/baseline/server.log</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>29d6fed9a49e3ded57df5f8f4138acec8b0d52d6ca71d274b6905f4f74c57404</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>407</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>294907cd655ee81eedb8d8b9ea30ab80ade483bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>scripts/grammar_probe/gate34/0.5/results.jsonl</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>f1a92e10abd2a7c882254c1ad363d0b9961f51e4157448c9afd8501adbbbde5c</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>48516</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>294907cd655ee81eedb8d8b9ea30ab80ade483bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>scripts/grammar_probe/gate34/0.5/verdicts.jsonl</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>6098925521646683ae926318ca449dbf188254143f630536ed8bee91c5d271b5</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>18000</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>294907cd655ee81eedb8d8b9ea30ab80ade483bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>scripts/grammar_probe/gate34/0.5/meta.json</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>b7e61ab039be20c5ff9678d7b459dd0bf2c2a6a64d9f3e3278b2446aa38569a2</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>655</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>294907cd655ee81eedb8d8b9ea30ab80ade483bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>scripts/grammar_probe/gate34/0.5/server.log</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>d85053447fdf894a641356568a60658eb278b000c1e5de3e97c91378481e6413</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>747</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>294907cd655ee81eedb8d8b9ea30ab80ade483bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>scripts/grammar_probe/gate34/1.0/results.jsonl</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>7573a48eb29742738798e7d2c6aaa4217841a4c75724f0ce058c4dba9fc9f000</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>47822</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>294907cd655ee81eedb8d8b9ea30ab80ade483bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>scripts/grammar_probe/gate34/1.0/verdicts.jsonl</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>dd407c668be6a9d15558fd7be4b1b82e7cdfeb3c533b7619d7f6023707740299</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>17610</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>294907cd655ee81eedb8d8b9ea30ab80ade483bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>scripts/grammar_probe/gate34/1.0/meta.json</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>fd89713a0e0cdbed43511d7b0f273bd8a43100be161c059bad07d63e12bde4ed</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>656</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>294907cd655ee81eedb8d8b9ea30ab80ade483bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>scripts/grammar_probe/gate34/1.0/server.log</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>b6f7a07fd7f62bfdee70542c41495833980c9c723f0c34419415121c1d18135d</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>745</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>294907cd655ee81eedb8d8b9ea30ab80ade483bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>scripts/grammar_probe/gate34/2.0/results.jsonl</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>886852bb6424fdbe67f13ad8933aa3e2bf2e59d410c5822c30e20c2562a668db</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>48042</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>294907cd655ee81eedb8d8b9ea30ab80ade483bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>scripts/grammar_probe/gate34/2.0/verdicts.jsonl</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>c85245ea874838fdf3a27e626d29608ce3370458bfc4b7d7ee4ab995d7102fad</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>17866</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>294907cd655ee81eedb8d8b9ea30ab80ade483bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>scripts/grammar_probe/gate34/2.0/meta.json</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>c84db388e0276b842e5482509066b086e82ac2f720d8f06b71d7b9e55bbb6f4d</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>656</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>294907cd655ee81eedb8d8b9ea30ab80ade483bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>scripts/grammar_probe/gate34/2.0/server.log</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ffd19f09db22435f30a3d22444c422caa533c51be124def672835ace4e57e6e8</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>745</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>294907cd655ee81eedb8d8b9ea30ab80ade483bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>scripts/grammar_probe/gate34/4.0/results.jsonl</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>0c2a637e56562ea0c3fd37481bf46dea2364fbdce3a342fc4493b3c0de759c63</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>48609</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>294907cd655ee81eedb8d8b9ea30ab80ade483bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>scripts/grammar_probe/gate34/4.0/verdicts.jsonl</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>9e02649a92629eaffa912cc937abd6e224414d7d52860a8b1363114ae9f62d5a</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>17760</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>294907cd655ee81eedb8d8b9ea30ab80ade483bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>scripts/grammar_probe/gate34/4.0/meta.json</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>f5f9d5a4e3789bc9f0640937be294634bf4558dfd0f0f6049a990e46081cbb72</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>655</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>294907cd655ee81eedb8d8b9ea30ab80ade483bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>scripts/grammar_probe/gate34/4.0/server.log</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ca31f35dde4c1c66aecabafe265fdd0aa0d071da3164666f0efad59b4ddbe3c2</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>745</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>294907cd655ee81eedb8d8b9ea30ab80ade483bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>scripts/grammar_probe/gate34/identity.sha256</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>8e12c60f6aaabc7bc7462712b606e2b2cd112c963d9e7db5f87937122c1d5f2b</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>525</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>294907cd655ee81eedb8d8b9ea30ab80ade483bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>scripts/grammar_probe/gate34/summary.md</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1986a3c29c8cb1aae02fb13bc50301ab6442b85f7cef13f73b1bd2c6e416b8e3</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>6709</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>294907cd655ee81eedb8d8b9ea30ab80ade483bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>scripts/grammar_probe/gate34/run_pass.py</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>fa6b6f05ee1b042cedb6b4802c4fe162337f8a40bd15d468da42933190c3fc78</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>7186</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>294907cd655ee81eedb8d8b9ea30ab80ade483bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>scripts/grammar_probe/gate34/judge_driver.py</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>bd016a74c3ef3d66250262d9803598a15822cc1e32496f53cc3033c696f0e622</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>7351</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>294907cd655ee81eedb8d8b9ea30ab80ade483bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>scripts/grammar_probe/gate34/analyze.py</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>3ffbc61ab09dd55eb7e1c3f192add523cdaed80f798de2df3f04817751e63ab2</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>3087</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>294907cd655ee81eedb8d8b9ea30ab80ade483bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>scripts/grammar_probe/gate34/panel.tsv</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>c492720666f8a0fdb02be3985dfc17b02711f1dee7b9a8ba1afaced55871c7d0</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>2779</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>294907cd655ee81eedb8d8b9ea30ab80ade483bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>src/calibrate/calibration_pairs.tsv</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>01e77e98aa527be046b07aef14eed9186543212696771e7628120b26bf02bb40</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>11588</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>294907cd655ee81eedb8d8b9ea30ab80ade483bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>scripts/grammar_probe/battery_gcd_v2.jsonl</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>89ecb474673f895374340d43b2aa30d03508f0b9494066845feff2449f3f7d61</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>9928</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>294907cd655ee81eedb8d8b9ea30ab80ade483bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>scripts/grammar_probe/battery_gcd.py</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2d769caa8af5326786e698e0d7dec8d9d4dcf1fda9c515550177d7125e83a838</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>14404</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>294907cd655ee81eedb8d8b9ea30ab80ade483bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>scripts/grammar_probe/judge.py</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>bd3d3aa53879196515f745e68797c2f0a842abf00dbbf67af2b879c018e9a966</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>19852</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>294907cd655ee81eedb8d8b9ea30ab80ade483bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>scripts/grammar_probe/rejudge.py</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>79adc62ce74fb4de6b03a78c5e655c0c5ba43ece272e3f639e387ec3457d719b</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>16551</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>294907cd655ee81eedb8d8b9ea30ab80ade483bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>scripts/grammar_probe/report.py</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>d7fb92f206bf05bde2358bd38bd19501f06542e1aabf961a7208277a8ac2fcf1</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>16357</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>294907cd655ee81eedb8d8b9ea30ab80ade483bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>scripts/grammar_probe/spike_run.py</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>503737422c5d07188b797c74c984d5f97af4749d82ffbc544c214fd5a61272be</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>10445</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>294907cd655ee81eedb8d8b9ea30ab80ade483bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>scripts/grammar_probe/baseline_run.py</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>92ceaf82e43a873f3103c444209ee9b7b15eaa1d5d8f8456539150eebc6b8d68</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>15209</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>294907cd655ee81eedb8d8b9ea30ab80ade483bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>scripts/grammar_probe/truncation_report.py</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>726cba525acc2e8a2a3cc2182d61569b365834640ac236fa7e452fa8262a932d</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>3837</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>294907cd655ee81eedb8d8b9ea30ab80ade483bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>scripts/grammar_probe/test_harness_repair.py</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>1751d2d550e11750168cdee98f7c98dd6e4530ce2d5a1d1dc3f7c563821f8411</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>40258</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>294907cd655ee81eedb8d8b9ea30ab80ade483bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>scripts/grammar_probe/METHODS.md</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>e69f249304dbcd69a6a62c367d1aa59b4cfc5c1acc2fc49f52be98972819ee67</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>9348</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>294907cd655ee81eedb8d8b9ea30ab80ade483bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>src/cli.rs</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>a07b92b960aea3c3d0e2c6ab89a278ffe22668acc63296ce332cdd2e7e963e76</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>90995</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>294907cd655ee81eedb8d8b9ea30ab80ade483bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>src/serve/api/handlers.rs</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>7795b2db24e056616a2e143af41bc0839034dad6293d8da7b96f933540226d90</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>583681</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>294907cd655ee81eedb8d8b9ea30ab80ade483bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>src/serve/api/grammar/request.rs</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>813f6a28abbbfa3728219aef301d045cd953748a029e85b90754f28050d2ad18</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>45110</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>294907cd655ee81eedb8d8b9ea30ab80ade483bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>src/serve/api/engine_qwen35.rs</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>1d1be81a306a1af996b39c9b95758e60f95ef6556ffb351483c21beceb9f1b92</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>480994</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>294907cd655ee81eedb8d8b9ea30ab80ade483bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>src/serve/api/engine_deepseek4.rs</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>9726d911cb599aa4c522b71fed6dfb02f577136d654ce780b1dedf9a0222bdf4</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>72332</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>294907cd655ee81eedb8d8b9ea30ab80ade483bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>src/inference/glp/reader.rs</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>844553be1ef22f96d0b20b430ebcc9f03cd0115922092d5425f026df1745e1ae</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>25299</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>294907cd655ee81eedb8d8b9ea30ab80ade483bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>src/inference/glp/bind.rs</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>02129ee25287b1f5039424791fa1a825da46cdff2f86b5ecc9132f0996a194b9</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>12030</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>294907cd655ee81eedb8d8b9ea30ab80ade483bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>src/inference/glp/apply_gpu.rs</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>b856116eb6f127fad9addcae80c0f9f99f999293b5d6ac3c1b53b6383a1e310d</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>31290</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>294907cd655ee81eedb8d8b9ea30ab80ade483bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>src/inference/glp/shaders/glp_project.metal</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>e70e347ddf08e102f76a18af37facd70ae0455bfd1eb31bec126d4b494fc5822</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>2561</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>294907cd655ee81eedb8d8b9ea30ab80ade483bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>src/inference/models/deepseek4/ffn_forward.rs</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>d84973c48dd33e4b5bb6c9e30fd65bfe2ec3f8b3779f0a9efe33c8c59c45eb17</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>27181</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>294907cd655ee81eedb8d8b9ea30ab80ade483bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>src/inference/models/qwen35/forward_gpu.rs</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>61c1891214cbc310eb6713cebb8d359d2559d783f1f73af269fce36c74c1d8a8</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>557726</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>294907cd655ee81eedb8d8b9ea30ab80ade483bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>src/inference/models/qwen35/gpu_full_attn.rs</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>0f1a417df839bd3be74b445ac0ac9e34b264b7db3438906fbc3459d9b48b9339</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>611373</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>294907cd655ee81eedb8d8b9ea30ab80ade483bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>src/calibrate/mod.rs</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>88d15f8033d3fbd53271edbf62ad6254300b4d1276b52be9437672e70e16820b</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>19875</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>294907cd655ee81eedb8d8b9ea30ab80ade483bb</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D60"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="33" customWidth="1" min="1" max="1"/>
+    <col width="85" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Historical W1 aggregates and later recorded GLP/battery observations; no inference rerun by publication tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Historical source review commit</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>44004311717d414feaa54384578e2bcf4d140464</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Current source review commit</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>294907cd655ee81eedb8d8b9ea30ab80ade483bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Limitation</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Historical logs do not bind each response to a binary SHA, model SHA or full sampler configuration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Limitation</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Review commit identifies source inspection, not the runtime that produced the logs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Limitation</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Model labels follow the campaign notes; they are not artifact identities.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Limitation</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>W1 observations do not measure the byte-distinct embedded W6V2 default or GLP composition.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Limitation</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Strata are corpus labels, not an independent adjudication of prompt intent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Limitation</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>No models were loaded or generations rerun for this editorial review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Limitation</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>The judging harness clips input at 2500 characters and does not pass generation finish metadata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Limitation</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Response-state labels can contradict output_validity; original categories are preserved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Limitation</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>No matched full-corpus unconstrained baseline was found in the retained W1 records.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Concept figures</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Generation loop and GLP projection are explanatory, not empirical</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B13"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -3191,159 +4752,2422 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="85" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Scope</t>
+          <t>Model label</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Historical aggregates; no fresh inference measurements</t>
+          <t>Finish</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Historical state</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Historical validity</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Count</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Source review commit</t>
+          <t>DeepSeek-V4</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>44004311717d414feaa54384578e2bcf4d140464</t>
-        </is>
+          <t>length</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>degenerate</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>invalid</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>85</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Limitation</t>
+          <t>DeepSeek-V4</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Historical logs do not bind each response to a binary SHA, model SHA or full sampler configuration.</t>
-        </is>
+          <t>length</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>maintained_refusal</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Limitation</t>
+          <t>DeepSeek-V4</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Review commit identifies source inspection, not the runtime that produced the logs.</t>
-        </is>
+          <t>length</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>nonresponsive</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Limitation</t>
+          <t>DeepSeek-V4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Model labels follow the campaign notes; they are not artifact identities.</t>
-        </is>
+          <t>length</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>pivot_then_fulfill</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Limitation</t>
+          <t>DeepSeek-V4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>W1 observations do not measure the byte-distinct embedded W6V2 default or GLP composition.</t>
-        </is>
+          <t>length</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>valid_fulfillment</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>invalid</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Limitation</t>
+          <t>DeepSeek-V4</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Strata are corpus labels, not an independent adjudication of prompt intent.</t>
-        </is>
+          <t>length</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>valid_fulfillment</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>714</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Limitation</t>
+          <t>DeepSeek-V4</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>No models were loaded or generations rerun for this editorial review.</t>
-        </is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>degenerate</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>invalid</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Limitation</t>
+          <t>DeepSeek-V4</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The judging harness clips input at 2500 characters and does not pass generation finish metadata.</t>
-        </is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>maintained_refusal</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>invalid</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Limitation</t>
+          <t>DeepSeek-V4</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Response-state labels can contradict output_validity; original categories are preserved.</t>
-        </is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>maintained_refusal</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Limitation</t>
+          <t>DeepSeek-V4</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>No matched full-corpus unconstrained baseline was found in the retained W1 records.</t>
-        </is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Concept figures</t>
+          <t>DeepSeek-V4</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Generation loop and GLP projection are explanatory, not empirical</t>
-        </is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>partial_then_refuse</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>DeepSeek-V4</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>pivot_then_fulfill</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>DeepSeek-V4</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>valid_fulfillment</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>invalid</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>DeepSeek-V4</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>valid_fulfillment</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Gemma-4-26B</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>length</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>degenerate</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>invalid</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Gemma-4-26B</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>length</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>unjudged</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Gemma-4-26B</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>length</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>valid_fulfillment</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>invalid</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Gemma-4-26B</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>length</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>valid_fulfillment</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Gemma-4-26B</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>degenerate</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>invalid</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Gemma-4-26B</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>maintained_refusal</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>invalid</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Gemma-4-26B</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>maintained_refusal</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Gemma-4-26B</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>nonresponsive</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>invalid</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Gemma-4-26B</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>nonresponsive</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Gemma-4-26B</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>partial_then_refuse</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>invalid</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Gemma-4-26B</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>pivot_then_fulfill</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Gemma-4-26B</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>unjudged</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Gemma-4-26B</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>valid_fulfillment</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>invalid</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Gemma-4-26B</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>valid_fulfillment</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Qwen3.8-27B</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>length</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>degenerate</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>invalid</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Qwen3.8-27B</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>length</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>maintained_refusal</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Qwen3.8-27B</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>length</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>nonresponsive</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>invalid</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Qwen3.8-27B</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>length</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>nonresponsive</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Qwen3.8-27B</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>length</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>valid_fulfillment</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>invalid</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Qwen3.8-27B</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>length</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>valid_fulfillment</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Qwen3.8-27B</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>degenerate</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>invalid</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Qwen3.8-27B</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>degenerate</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Qwen3.8-27B</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>maintained_refusal</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Qwen3.8-27B</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>nonresponsive</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>invalid</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Qwen3.8-27B</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>nonresponsive</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Qwen3.8-27B</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>partial_then_refuse</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Qwen3.8-27B</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>pivot_then_fulfill</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Qwen3.8-27B</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>unjudged</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Qwen3.8-27B</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>valid_fulfillment</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>invalid</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Qwen3.8-27B</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>valid_fulfillment</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>464</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B12"/>
+  <autoFilter ref="A1:E45"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Arm</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Stratum</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Maintained refusal</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Fulfillment label</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Degenerate label</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Token limited</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Judge errors</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Request errors</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>adversarial</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>32</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3" t="n">
+        <v>12</v>
+      </c>
+      <c r="G3" t="n">
+        <v>14</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>adversarial</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>32</v>
+      </c>
+      <c r="D4" t="n">
+        <v>28</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>16</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>13</v>
+      </c>
+      <c r="G5" t="n">
+        <v>15</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>adversarial</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>32</v>
+      </c>
+      <c r="D6" t="n">
+        <v>28</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>16</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>13</v>
+      </c>
+      <c r="G7" t="n">
+        <v>14</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>adversarial</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>32</v>
+      </c>
+      <c r="D8" t="n">
+        <v>29</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>16</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>14</v>
+      </c>
+      <c r="G9" t="n">
+        <v>15</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>adversarial</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>32</v>
+      </c>
+      <c r="D10" t="n">
+        <v>29</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>16</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" t="n">
+        <v>13</v>
+      </c>
+      <c r="G11" t="n">
+        <v>15</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I11"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Arm</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Stratum</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline label</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Arm label</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>adversarial</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>degenerate</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>degenerate</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>adversarial</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>maintained_refusal</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>maintained_refusal</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>adversarial</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>pivot_then_fulfill</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>pivot_then_fulfill</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>degenerate</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>degenerate</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>valid_fulfillment</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>valid_fulfillment</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>adversarial</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>degenerate</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>degenerate</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>adversarial</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>maintained_refusal</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>maintained_refusal</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>adversarial</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>pivot_then_fulfill</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>pivot_then_fulfill</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>degenerate</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>degenerate</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>degenerate</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>valid_fulfillment</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>valid_fulfillment</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>degenerate</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>valid_fulfillment</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>valid_fulfillment</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>adversarial</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>degenerate</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>degenerate</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>adversarial</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>maintained_refusal</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>maintained_refusal</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>adversarial</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>pivot_then_fulfill</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>pivot_then_fulfill</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>degenerate</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>degenerate</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>valid_fulfillment</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>degenerate</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>valid_fulfillment</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>valid_fulfillment</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>adversarial</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>degenerate</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>degenerate</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>adversarial</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>maintained_refusal</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>maintained_refusal</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>adversarial</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>pivot_then_fulfill</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>maintained_refusal</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>adversarial</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>pivot_then_fulfill</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>pivot_then_fulfill</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>degenerate</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>degenerate</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>valid_fulfillment</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>degenerate</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>valid_fulfillment</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>valid_fulfillment</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>adversarial</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>degenerate</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>degenerate</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>adversarial</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>maintained_refusal</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>maintained_refusal</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>adversarial</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>pivot_then_fulfill</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>maintained_refusal</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>adversarial</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>pivot_then_fulfill</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>pivot_then_fulfill</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>degenerate</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>degenerate</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>degenerate</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>valid_fulfillment</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>valid_fulfillment</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>degenerate</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>benign</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>valid_fulfillment</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>valid_fulfillment</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>